--- a/results/reliability_eval/reliability_eval_typo-test-09-30/Llama-3-8B_P17_char_repetition_typo3_sample_tok25_temp0.1_direct_completion_rep5_beams5_maxent20_rows100_scores_typo-test-09-30.xlsx
+++ b/results/reliability_eval/reliability_eval_typo-test-09-30/Llama-3-8B_P17_char_repetition_typo3_sample_tok25_temp0.1_direct_completion_rep5_beams5_maxent20_rows100_scores_typo-test-09-30.xlsx
@@ -512,52 +512,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.7878416972664218</v>
+        <v>0.8675881410256411</v>
       </c>
       <c r="B2" t="n">
-        <v>0.7798712471960304</v>
+        <v>0.873858359133127</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2081302341750849</v>
+        <v>0.160839507061502</v>
       </c>
       <c r="D2" t="n">
-        <v>3.903638162354357</v>
+        <v>0.4553810823257502</v>
       </c>
       <c r="E2" t="n">
-        <v>20.51351854241907</v>
+        <v>33.52348707090734</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7366381068951446</v>
+        <v>0.6682692307692308</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7695357747746936</v>
+        <v>0.800799931943549</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4117091824046642</v>
+        <v>0.4937401071158194</v>
       </c>
       <c r="I2" t="n">
-        <v>4.755578136496308</v>
+        <v>1.827921403131182</v>
       </c>
       <c r="J2" t="n">
-        <v>4.14256444864214</v>
+        <v>5.769651727207126</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9967360261117911</v>
+        <v>0.9967948717948718</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9960925039872408</v>
+        <v>0.9948484848484849</v>
       </c>
       <c r="M2" t="n">
         <v>0.02</v>
       </c>
       <c r="N2" t="n">
-        <v>0.05867070452737242</v>
+        <v>0.05867070452737241</v>
       </c>
       <c r="O2" t="n">
-        <v>3.498609153391897</v>
+        <v>4.965784276727264</v>
       </c>
       <c r="P2" t="n">
-        <v>0.57</v>
+        <v>0.48</v>
       </c>
     </row>
   </sheetData>
